--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20288,7 +20288,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22210,7 +22210,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22396,7 +22396,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22582,7 +22582,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22892,7 +22892,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23450,7 +23450,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23760,7 +23760,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23946,7 +23946,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24008,7 +24008,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24380,7 +24380,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24814,7 +24814,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25000,7 +25000,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25248,7 +25248,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25372,7 +25372,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25930,7 +25930,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26612,7 +26612,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27356,7 +27356,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27604,7 +27604,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27790,7 +27790,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28720,7 +28720,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28844,7 +28844,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -29111,7 +29111,7 @@
           <t>A | 417呎 (2房)
 $1093万
 $26,200/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -29119,7 +29119,7 @@
           <t>B | 369呎 (1房)
 $1077万
 $29,200/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -29127,7 +29127,7 @@
           <t>C | 284呎 (1房)
 $795万
 $28,000/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -29135,7 +29135,7 @@
           <t>D | 411呎 (2房)
 $1143万
 $27,800/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -29143,7 +29143,7 @@
           <t>E | 276呎 (1房)
 $731万
 $26,500/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -29151,7 +29151,7 @@
           <t>F | 266呎 (1房)
 $670万
 $25,169/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -29159,7 +29159,7 @@
           <t>G | 262呎 (1房)
 $673万
 $25,700/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -29167,7 +29167,7 @@
           <t>H | 262呎 (1房)
 $673万
 $25,700/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -29175,7 +29175,7 @@
           <t>J | 262呎 (1房)
 $687万
 $26,214/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -29183,7 +29183,7 @@
           <t>K | 262呎 (1房)
 $668万
 $25,500/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -29191,7 +29191,7 @@
           <t>L | 266呎 (1房)
 $708万
 $26,600/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -29199,7 +29199,7 @@
           <t>M | 266呎 (1房)
 $716万
 $26,900/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -29207,7 +29207,7 @@
           <t>N | 642呎 (3房)
 $2183万
 $34,000/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -29251,7 +29251,7 @@
           <t>A | 417呎 (2房)
 $862万
 $20,674/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -29259,7 +29259,7 @@
           <t>B | 369呎 (1房)
 $830万
 $22,496/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -29267,7 +29267,7 @@
           <t>C | 284呎 (1房)
 $564万
 $19,853/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -29275,7 +29275,7 @@
           <t>D | 411呎 (2房)
 $843万
 $20,503/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -29283,7 +29283,7 @@
           <t>E | 276呎 (1房)
 $547万
 $19,813/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -29291,7 +29291,7 @@
           <t>F | 266呎 (1房)
 $495万
 $18,611/呎
-(25年-04月-21日)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -29299,7 +29299,7 @@
           <t>G | 262呎 (1房)
 $523万
 $19,955/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -29307,7 +29307,7 @@
           <t>H | 262呎 (1房)
 $518万
 $19,763/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>J | 262呎 (1房)
 $518万
 $19,763/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>K | 262呎 (1房)
 $523万
 $19,955/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -29331,7 +29331,7 @@
           <t>L | 266呎 (1房)
 $520万
 $19,536/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -29339,7 +29339,7 @@
           <t>M | 266呎 (1房)
 $522万
 $19,630/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -29347,7 +29347,7 @@
           <t>N | 251呎 (1房)
 $533万
 $21,245/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -29398,7 +29398,7 @@
           <t>A | 417呎 (2房)
 $857万
 $20,553/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -29406,7 +29406,7 @@
           <t>B | 369呎 (1房)
 $825万
 $22,370/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -29414,7 +29414,7 @@
           <t>C | 284呎 (1房)
 $561万
 $19,738/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -29422,7 +29422,7 @@
           <t>D | 411呎 (2房)
 $838万
 $20,387/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -29430,7 +29430,7 @@
           <t>E | 276呎 (1房)
 $553万
 $20,028/呎
-(24年-07月-29日)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -29438,7 +29438,7 @@
           <t>F | 266呎 (1房)
 $492万
 $18,502/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -29446,7 +29446,7 @@
           <t>G | 262呎 (1房)
 $520万
 $19,840/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -29454,7 +29454,7 @@
           <t>H | 262呎 (1房)
 $515万
 $19,648/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -29462,7 +29462,7 @@
           <t>J | 262呎 (1房)
 $506万
 $19,326/呎
-(24年-09月-25日)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -29470,7 +29470,7 @@
           <t>K | 262呎 (1房)
 $503万
 $19,189/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -29478,7 +29478,7 @@
           <t>L | 266呎 (1房)
 $528万
 $19,862/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -29486,7 +29486,7 @@
           <t>M | 266呎 (1房)
 $537万
 $20,178/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -29494,7 +29494,7 @@
           <t>N | 260呎 (1房)
 $530万
 $20,390/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -29502,7 +29502,7 @@
           <t>P | 314呎 (1房)
 $609万
 $19,400/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="P7" s="20" t="inlineStr">
@@ -29510,7 +29510,7 @@
           <t>Q | 430呎 (3房)
 $843万
 $19,614/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="Q7" s="20" t="inlineStr">
@@ -29518,7 +29518,7 @@
           <t>R | 346呎 (2房)
 $669万
 $19,342/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="R7" s="20" t="inlineStr">
@@ -29526,7 +29526,7 @@
           <t>S | 269呎 (1房)
 $499万
 $18,555/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="S7" s="20" t="inlineStr">
@@ -29534,7 +29534,7 @@
           <t>T | 263呎 (1房)
 $532万
 $20,224/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="T7" s="20" t="inlineStr">
@@ -29542,7 +29542,7 @@
           <t>U | 262呎 (1房)
 $557万
 $21,258/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="U7" s="20" t="inlineStr">
@@ -29550,7 +29550,7 @@
           <t>V | 262呎 (1房)
 $537万
 $20,503/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="V7" s="20" t="inlineStr">
@@ -29558,7 +29558,7 @@
           <t>W | 270呎 (1房)
 $562万
 $20,832/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -29573,7 +29573,7 @@
           <t>A | 417呎 (2房)
 $855万
 $20,493/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -29581,7 +29581,7 @@
           <t>B | 369呎 (1房)
 $821万
 $22,242/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -29589,7 +29589,7 @@
           <t>C | 284呎 (1房)
 $557万
 $19,623/呎
-(25年-02月-24日)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -29597,7 +29597,7 @@
           <t>D | 411呎 (2房)
 $847万
 $20,615/呎
-(24年-12月-01日)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -29605,7 +29605,7 @@
           <t>E | 276呎 (1房)
 $551万
 $19,970/呎
-(24年-08月-25日)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -29613,7 +29613,7 @@
           <t>F | 266呎 (1房)
 $499万
 $18,761/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -29621,7 +29621,7 @@
           <t>G | 262呎 (1房)
 $527万
 $20,108/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -29629,7 +29629,7 @@
           <t>H | 262呎 (1房)
 $522万
 $19,913/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -29637,7 +29637,7 @@
           <t>J | 262呎 (1房)
 $505万
 $19,271/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -29645,7 +29645,7 @@
           <t>K | 262呎 (1房)
 $516万
 $19,676/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -29653,7 +29653,7 @@
           <t>L | 266呎 (1房)
 $525万
 $19,743/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -29661,7 +29661,7 @@
           <t>M | 266呎 (1房)
 $534万
 $20,058/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -29669,7 +29669,7 @@
           <t>N | 260呎 (1房)
 $527万
 $20,267/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -29677,7 +29677,7 @@
           <t>P | 314呎 (1房)
 $602万
 $19,181/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -29685,7 +29685,7 @@
           <t>Q | 430呎 (3房)
 $838万
 $19,499/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="Q8" s="20" t="inlineStr">
@@ -29693,7 +29693,7 @@
           <t>R | 346呎 (2房)
 $677万
 $19,558/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="R8" s="20" t="inlineStr">
@@ -29701,7 +29701,7 @@
           <t>S | 269呎 (1房)
 $496万
 $18,446/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="S8" s="20" t="inlineStr">
@@ -29709,7 +29709,7 @@
           <t>T | 263呎 (1房)
 $529万
 $20,102/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="T8" s="20" t="inlineStr">
@@ -29717,7 +29717,7 @@
           <t>U | 262呎 (1房)
 $554万
 $21,131/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="U8" s="20" t="inlineStr">
@@ -29725,7 +29725,7 @@
           <t>V | 262呎 (1房)
 $534万
 $20,385/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="V8" s="20" t="inlineStr">
@@ -29733,7 +29733,7 @@
           <t>W | 270呎 (1房)
 $559万
 $20,711/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -29748,7 +29748,7 @@
           <t>A | 417呎 (2房)
 $852万
 $20,433/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -29756,7 +29756,7 @@
           <t>B | 369呎 (1房)
 $816万
 $22,113/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -29764,7 +29764,7 @@
           <t>C | 284呎 (1房)
 $554万
 $19,507/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -29772,7 +29772,7 @@
           <t>D | 411呎 (2房)
 $828万
 $20,155/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -29780,7 +29780,7 @@
           <t>E | 276呎 (1房)
 $549万
 $19,908/呎
-(24年-07月-07日)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -29788,7 +29788,7 @@
           <t>F | 266呎 (1房)
 $498万
 $18,704/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -29796,7 +29796,7 @@
           <t>G | 262呎 (1房)
 $525万
 $20,052/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -29804,7 +29804,7 @@
           <t>H | 262呎 (1房)
 $520万
 $19,856/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -29812,7 +29812,7 @@
           <t>J | 262呎 (1房)
 $495万
 $18,895/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -29820,7 +29820,7 @@
           <t>K | 262呎 (1房)
 $511万
 $19,513/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -29828,7 +29828,7 @@
           <t>L | 266呎 (1房)
 $522万
 $19,627/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -29836,7 +29836,7 @@
           <t>M | 266呎 (1房)
 $530万
 $19,941/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -29844,7 +29844,7 @@
           <t>N | 260呎 (1房)
 $524万
 $20,144/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -29852,7 +29852,7 @@
           <t>P | 314呎 (1房)
 $599万
 $19,069/呎
-(24年-12月-23日)</t>
+(24年-12月-24日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -29860,7 +29860,7 @@
           <t>Q | 430呎 (3房)
 $833万
 $19,383/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="Q9" s="20" t="inlineStr">
@@ -29868,7 +29868,7 @@
           <t>R | 346呎 (2房)
 $675万
 $19,501/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="R9" s="20" t="inlineStr">
@@ -29876,7 +29876,7 @@
           <t>S | 269呎 (1房)
 $495万
 $18,391/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="S9" s="20" t="inlineStr">
@@ -29884,7 +29884,7 @@
           <t>T | 263呎 (1房)
 $527万
 $20,043/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="T9" s="20" t="inlineStr">
@@ -29892,7 +29892,7 @@
           <t>U | 262呎 (1房)
 $550万
 $21,006/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="U9" s="20" t="inlineStr">
@@ -29900,7 +29900,7 @@
           <t>V | 262呎 (1房)
 $531万
 $20,263/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="V9" s="20" t="inlineStr">
@@ -29908,7 +29908,7 @@
           <t>W | 270呎 (1房)
 $545万
 $20,184/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -29923,7 +29923,7 @@
           <t>A | 417呎 (2房)
 $850万
 $20,373/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -29931,7 +29931,7 @@
           <t>B | 369呎 (1房)
 $814万
 $22,050/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -29939,7 +29939,7 @@
           <t>C | 284呎 (1房)
 $552万
 $19,451/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -29947,7 +29947,7 @@
           <t>D | 411呎 (2房)
 $826万
 $20,097/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -29955,7 +29955,7 @@
           <t>E | 276呎 (1房)
 $548万
 $19,849/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -29963,7 +29963,7 @@
           <t>F | 266呎 (1房)
 $496万
 $18,650/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -29971,7 +29971,7 @@
           <t>G | 262呎 (1房)
 $524万
 $19,995/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -29979,7 +29979,7 @@
           <t>H | 262呎 (1房)
 $519万
 $19,800/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -29987,7 +29987,7 @@
           <t>J | 262呎 (1房)
 $494万
 $18,842/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -29995,7 +29995,7 @@
           <t>K | 262呎 (1房)
 $499万
 $19,027/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -30003,7 +30003,7 @@
           <t>L | 266呎 (1房)
 $509万
 $19,134/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -30011,7 +30011,7 @@
           <t>M | 266呎 (1房)
 $511万
 $19,227/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -30019,7 +30019,7 @@
           <t>N | 260呎 (1房)
 $522万
 $20,084/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -30027,7 +30027,7 @@
           <t>P | 314呎 (1房)
 $587万
 $18,697/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr">
@@ -30035,7 +30035,7 @@
           <t>Q | 430呎 (3房)
 $831万
 $19,326/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="Q10" s="20" t="inlineStr">
@@ -30043,7 +30043,7 @@
           <t>R | 346呎 (2房)
 $673万
 $19,446/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="R10" s="20" t="inlineStr">
@@ -30051,7 +30051,7 @@
           <t>S | 269呎 (1房)
 $493万
 $18,338/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="S10" s="20" t="inlineStr">
@@ -30059,7 +30059,7 @@
           <t>T | 263呎 (1房)
 $526万
 $19,984/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="T10" s="20" t="inlineStr">
@@ -30067,7 +30067,7 @@
           <t>U | 262呎 (1房)
 $547万
 $20,882/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="U10" s="20" t="inlineStr">
@@ -30075,7 +30075,7 @@
           <t>V | 262呎 (1房)
 $528万
 $20,144/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="V10" s="20" t="inlineStr">
@@ -30083,7 +30083,7 @@
           <t>W | 270呎 (1房)
 $542万
 $20,067/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
     </row>
@@ -30098,7 +30098,7 @@
           <t>A | 417呎 (2房)
 $847万
 $20,313/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -30106,7 +30106,7 @@
           <t>B | 369呎 (1房)
 $811万
 $21,987/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -30114,7 +30114,7 @@
           <t>C | 284呎 (1房)
 $551万
 $19,392/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30122,7 +30122,7 @@
           <t>D | 411呎 (2房)
 $824万
 $20,038/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -30130,7 +30130,7 @@
           <t>E | 276呎 (1房)
 $546万
 $19,790/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -30138,7 +30138,7 @@
           <t>F | 266呎 (1房)
 $486万
 $18,282/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -30146,7 +30146,7 @@
           <t>G | 262呎 (1房)
 $522万
 $19,938/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -30154,7 +30154,7 @@
           <t>H | 262呎 (1房)
 $517万
 $19,743/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -30162,7 +30162,7 @@
           <t>J | 262呎 (1房)
 $492万
 $18,787/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -30170,7 +30170,7 @@
           <t>K | 262呎 (1房)
 $497万
 $18,973/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -30178,7 +30178,7 @@
           <t>L | 266呎 (1房)
 $519万
 $19,508/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -30186,7 +30186,7 @@
           <t>M | 266呎 (1房)
 $510万
 $19,170/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -30194,7 +30194,7 @@
           <t>N | 260呎 (1房)
 $521万
 $20,024/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -30202,7 +30202,7 @@
           <t>P | 314呎 (1房)
 $599万
 $19,062/呎
-(25年-02月-26日)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
@@ -30210,7 +30210,7 @@
           <t>Q | 430呎 (3房)
 $857万
 $19,921/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="Q11" s="20" t="inlineStr">
@@ -30218,7 +30218,7 @@
           <t>R | 346呎 (2房)
 $660万
 $19,066/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="R11" s="20" t="inlineStr">
@@ -30226,7 +30226,7 @@
           <t>S | 269呎 (1房)
 $492万
 $18,282/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="S11" s="20" t="inlineStr">
@@ -30234,7 +30234,7 @@
           <t>T | 263呎 (1房)
 $524万
 $19,925/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="T11" s="20" t="inlineStr">
@@ -30242,7 +30242,7 @@
           <t>U | 262呎 (1房)
 $544万
 $20,758/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="U11" s="20" t="inlineStr">
@@ -30250,7 +30250,7 @@
           <t>V | 262呎 (1房)
 $525万
 $20,021/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="V11" s="20" t="inlineStr">
@@ -30258,7 +30258,7 @@
           <t>W | 270呎 (1房)
 $539万
 $19,947/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -30273,7 +30273,7 @@
           <t>A | 417呎 (2房)
 $828万
 $19,867/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -30281,7 +30281,7 @@
           <t>B | 369呎 (1房)
 $809万
 $21,922/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -30289,7 +30289,7 @@
           <t>C | 284呎 (1房)
 $549万
 $19,336/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -30297,7 +30297,7 @@
           <t>D | 411呎 (2房)
 $821万
 $19,980/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -30305,7 +30305,7 @@
           <t>E | 276呎 (1房)
 $535万
 $19,399/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -30313,7 +30313,7 @@
           <t>F | 266呎 (1房)
 $485万
 $18,229/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -30321,7 +30321,7 @@
           <t>G | 262呎 (1房)
 $512万
 $19,557/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -30329,7 +30329,7 @@
           <t>H | 262呎 (1房)
 $507万
 $19,365/呎
-(25年-11月-21日)</t>
+(25年-11月-22日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -30337,7 +30337,7 @@
           <t>J | 262呎 (1房)
 $507万
 $19,365/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -30345,7 +30345,7 @@
           <t>K | 262呎 (1房)
 $512万
 $19,557/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -30353,7 +30353,7 @@
           <t>L | 266呎 (1房)
 $517万
 $19,450/呎
-(25年-09月-19日)</t>
+(25年-09月-20日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -30361,7 +30361,7 @@
           <t>M | 266呎 (1房)
 $520万
 $19,546/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -30369,7 +30369,7 @@
           <t>N | 260呎 (1房)
 $519万
 $19,964/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -30377,7 +30377,7 @@
           <t>P | 314呎 (1房)
 $584万
 $18,588/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr">
@@ -30385,7 +30385,7 @@
           <t>Q | 430呎 (3房)
 $854万
 $19,862/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="Q12" s="20" t="inlineStr">
@@ -30393,7 +30393,7 @@
           <t>R | 346呎 (2房)
 $658万
 $19,012/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="R12" s="20" t="inlineStr">
@@ -30401,7 +30401,7 @@
           <t>S | 269呎 (1房)
 $490万
 $18,229/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="S12" s="20" t="inlineStr">
@@ -30409,7 +30409,7 @@
           <t>T | 263呎 (1房)
 $522万
 $19,862/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="T12" s="20" t="inlineStr">
@@ -30417,7 +30417,7 @@
           <t>U | 262呎 (1房)
 $541万
 $20,634/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="U12" s="20" t="inlineStr">
@@ -30425,7 +30425,7 @@
           <t>V | 262呎 (1房)
 $521万
 $19,903/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="V12" s="20" t="inlineStr">
@@ -30433,7 +30433,7 @@
           <t>W | 270呎 (1房)
 $535万
 $19,830/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -30448,7 +30448,7 @@
           <t>A | 417呎 (2房)
 $849万
 $20,348/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -30456,7 +30456,7 @@
           <t>B | 369呎 (1房)
 $807万
 $21,859/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -30464,7 +30464,7 @@
           <t>C | 284呎 (1房)
 $547万
 $19,277/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -30472,7 +30472,7 @@
           <t>D | 411呎 (2房)
 $819万
 $19,922/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -30480,7 +30480,7 @@
           <t>E | 276呎 (1房)
 $543万
 $19,670/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -30488,7 +30488,7 @@
           <t>F | 266呎 (1房)
 $483万
 $18,176/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -30496,7 +30496,7 @@
           <t>G | 262呎 (1房)
 $511万
 $19,501/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -30504,7 +30504,7 @@
           <t>H | 262呎 (1房)
 $506万
 $19,309/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -30512,7 +30512,7 @@
           <t>J | 262呎 (1房)
 $498万
 $18,993/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -30520,7 +30520,7 @@
           <t>K | 262呎 (1房)
 $503万
 $19,182/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -30528,7 +30528,7 @@
           <t>L | 266呎 (1房)
 $516万
 $19,393/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -30536,7 +30536,7 @@
           <t>M | 266呎 (1房)
 $518万
 $19,488/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -30544,7 +30544,7 @@
           <t>N | 260呎 (1房)
 $517万
 $19,901/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -30552,7 +30552,7 @@
           <t>P | 314呎 (1房)
 $582万
 $18,531/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
@@ -30560,7 +30560,7 @@
           <t>Q | 430呎 (3房)
 $851万
 $19,802/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="Q13" s="20" t="inlineStr">
@@ -30568,7 +30568,7 @@
           <t>R | 346呎 (2房)
 $656万
 $18,956/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="R13" s="20" t="inlineStr">
@@ -30576,7 +30576,7 @@
           <t>S | 269呎 (1房)
 $489万
 $18,174/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="S13" s="20" t="inlineStr">
@@ -30584,7 +30584,7 @@
           <t>T | 263呎 (1房)
 $521万
 $19,803/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="T13" s="20" t="inlineStr">
@@ -30592,7 +30592,7 @@
           <t>U | 262呎 (1房)
 $539万
 $20,570/呎
-(26年-01月-10日)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="U13" s="20" t="inlineStr">
@@ -30600,7 +30600,7 @@
           <t>V | 262呎 (1房)
 $520万
 $19,840/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="V13" s="20" t="inlineStr">
@@ -30608,7 +30608,7 @@
           <t>W | 270呎 (1房)
 $534万
 $19,771/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -30623,7 +30623,7 @@
           <t>A | 417呎 (2房)
 $824万
 $19,748/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -30631,7 +30631,7 @@
           <t>B | 369呎 (1房)
 $776万
 $21,022/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -30639,7 +30639,7 @@
           <t>C | 284呎 (1房)
 $546万
 $19,217/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -30647,7 +30647,7 @@
           <t>D | 411呎 (2房)
 $816万
 $19,864/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -30655,7 +30655,7 @@
           <t>E | 276呎 (1房)
 $541万
 $19,611/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -30663,7 +30663,7 @@
           <t>F | 266呎 (1房)
 $482万
 $18,119/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -30671,7 +30671,7 @@
           <t>G | 262呎 (1房)
 $518万
 $19,764/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -30679,7 +30679,7 @@
           <t>H | 262呎 (1房)
 $513万
 $19,569/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -30687,7 +30687,7 @@
           <t>J | 262呎 (1房)
 $496万
 $18,938/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -30695,7 +30695,7 @@
           <t>K | 262呎 (1房)
 $493万
 $18,808/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -30703,7 +30703,7 @@
           <t>L | 266呎 (1房)
 $514万
 $19,332/呎
-(25年-09月-19日)</t>
+(25年-09月-20日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -30711,7 +30711,7 @@
           <t>M | 266呎 (1房)
 $517万
 $19,427/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -30719,7 +30719,7 @@
           <t>N | 260呎 (1房)
 $516万
 $19,841/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -30727,7 +30727,7 @@
           <t>P | 314呎 (1房)
 $580万
 $18,475/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr">
@@ -30735,7 +30735,7 @@
           <t>Q | 430呎 (3房)
 $821万
 $19,095/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="Q14" s="20" t="inlineStr">
@@ -30743,7 +30743,7 @@
           <t>R | 346呎 (2房)
 $654万
 $18,899/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="R14" s="20" t="inlineStr">
@@ -30751,7 +30751,7 @@
           <t>S | 269呎 (1房)
 $498万
 $18,530/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="S14" s="20" t="inlineStr">
@@ -30759,7 +30759,7 @@
           <t>T | 263呎 (1房)
 $519万
 $19,744/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="T14" s="20" t="inlineStr">
@@ -30767,7 +30767,7 @@
           <t>U | 262呎 (1房)
 $537万
 $20,506/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="U14" s="20" t="inlineStr">
@@ -30775,7 +30775,7 @@
           <t>V | 262呎 (1房)
 $518万
 $19,781/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="V14" s="20" t="inlineStr">
@@ -30783,7 +30783,7 @@
           <t>W | 270呎 (1房)
 $524万
 $19,391/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -30798,7 +30798,7 @@
           <t>A | 417呎 (2房)
 $835万
 $20,014/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -30806,7 +30806,7 @@
           <t>B | 369呎 (1房)
 $773万
 $20,960/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -30814,7 +30814,7 @@
           <t>C | 284呎 (1房)
 $544万
 $19,161/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -30822,7 +30822,7 @@
           <t>D | 411呎 (2房)
 $814万
 $19,806/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -30830,7 +30830,7 @@
           <t>E | 276呎 (1房)
 $552万
 $19,983/呎
-(24年-07月-04日)</t>
+(24年-07月-05日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -30838,7 +30838,7 @@
           <t>F | 266呎 (1房)
 $489万
 $18,372/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -30846,7 +30846,7 @@
           <t>G | 262呎 (1房)
 $516万
 $19,707/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -30854,7 +30854,7 @@
           <t>H | 262呎 (1房)
 $511万
 $19,512/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -30862,7 +30862,7 @@
           <t>J | 262呎 (1房)
 $486万
 $18,568/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -30870,7 +30870,7 @@
           <t>K | 262呎 (1房)
 $491万
 $18,754/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -30878,7 +30878,7 @@
           <t>L | 266呎 (1房)
 $513万
 $19,274/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -30886,7 +30886,7 @@
           <t>M | 266呎 (1房)
 $515万
 $19,369/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -30894,7 +30894,7 @@
           <t>N | 260呎 (1房)
 $514万
 $19,782/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -30902,7 +30902,7 @@
           <t>P | 314呎 (1房)
 $578万
 $18,421/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr">
@@ -30910,7 +30910,7 @@
           <t>Q | 430呎 (3房)
 $846万
 $19,683/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="Q15" s="20" t="inlineStr">
@@ -30918,7 +30918,7 @@
           <t>R | 346呎 (2房)
 $663万
 $19,165/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="R15" s="20" t="inlineStr">
@@ -30926,7 +30926,7 @@
           <t>S | 269呎 (1房)
 $497万
 $18,473/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="S15" s="20" t="inlineStr">
@@ -30934,7 +30934,7 @@
           <t>T | 263呎 (1房)
 $518万
 $19,684/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="T15" s="20" t="inlineStr">
@@ -30942,7 +30942,7 @@
           <t>U | 262呎 (1房)
 $536万
 $20,446/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="U15" s="20" t="inlineStr">
@@ -30950,7 +30950,7 @@
           <t>V | 262呎 (1房)
 $517万
 $19,721/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="V15" s="20" t="inlineStr">
@@ -30958,7 +30958,7 @@
           <t>W | 270呎 (1房)
 $522万
 $19,333/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -30973,7 +30973,7 @@
           <t>A | 417呎 (2房)
 $819万
 $19,632/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>B | 369呎 (1房)
 $769万
 $20,839/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -30989,7 +30989,7 @@
           <t>C | 284呎 (1房)
 $541万
 $19,046/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -30997,7 +30997,7 @@
           <t>D | 411呎 (2房)
 $809万
 $19,690/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -31005,7 +31005,7 @@
           <t>E | 276呎 (1房)
 $538万
 $19,490/呎
-(24年-07月-11日)</t>
+(24年-07月-12日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -31013,7 +31013,7 @@
           <t>F | 266呎 (1房)
 $503万
 $18,925/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -31021,7 +31021,7 @@
           <t>G | 262呎 (1房)
 $525万
 $20,041/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -31029,7 +31029,7 @@
           <t>H | 262呎 (1房)
 $520万
 $19,842/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -31037,7 +31037,7 @@
           <t>J | 262呎 (1房)
 $502万
 $19,142/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -31045,7 +31045,7 @@
           <t>K | 262呎 (1房)
 $507万
 $19,334/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -31053,7 +31053,7 @@
           <t>L | 266呎 (1房)
 $500万
 $18,791/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -31061,7 +31061,7 @@
           <t>M | 266呎 (1房)
 $502万
 $18,884/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -31069,7 +31069,7 @@
           <t>N | 260呎 (1房)
 $513万
 $19,722/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -31077,7 +31077,7 @@
           <t>P | 314呎 (1房)
 $577万
 $18,365/呎
-(25年-02月-24日)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr">
@@ -31085,7 +31085,7 @@
           <t>Q | 430呎 (3房)
 $816万
 $18,980/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="Q16" s="20" t="inlineStr">
@@ -31093,7 +31093,7 @@
           <t>R | 346呎 (2房)
 $661万
 $19,108/呎
-(24年-12月-01日)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="R16" s="20" t="inlineStr">
@@ -31101,7 +31101,7 @@
           <t>S | 269呎 (1房)
 $485万
 $18,012/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="S16" s="20" t="inlineStr">
@@ -31109,7 +31109,7 @@
           <t>T | 263呎 (1房)
 $516万
 $19,622/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="T16" s="20" t="inlineStr">
@@ -31117,7 +31117,7 @@
           <t>U | 262呎 (1房)
 $534万
 $20,382/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="U16" s="20" t="inlineStr">
@@ -31125,7 +31125,7 @@
           <t>V | 262呎 (1房)
 $498万
 $19,014/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="V16" s="20" t="inlineStr">
@@ -31133,7 +31133,7 @@
           <t>W | 270呎 (1房)
 $529万
 $19,592/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -31148,7 +31148,7 @@
           <t>A | 417呎 (2房)
 $819万
 $19,632/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -31156,7 +31156,7 @@
           <t>B | 369呎 (1房)
 $762万
 $20,653/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -31164,7 +31164,7 @@
           <t>C | 284呎 (1房)
 $536万
 $18,871/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -31172,7 +31172,7 @@
           <t>D | 411呎 (2房)
 $802万
 $19,515/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -31180,7 +31180,7 @@
           <t>E | 276呎 (1房)
 $536万
 $19,432/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -31188,7 +31188,7 @@
           <t>F | 266呎 (1房)
 $502万
 $18,869/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -31196,7 +31196,7 @@
           <t>G | 262呎 (1房)
 $524万
 $19,984/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -31204,7 +31204,7 @@
           <t>H | 262呎 (1房)
 $518万
 $19,785/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -31212,7 +31212,7 @@
           <t>J | 262呎 (1房)
 $500万
 $19,082/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -31220,7 +31220,7 @@
           <t>K | 262呎 (1房)
 $488万
 $18,642/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -31228,7 +31228,7 @@
           <t>L | 266呎 (1房)
 $497万
 $18,675/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -31236,7 +31236,7 @@
           <t>M | 266呎 (1房)
 $499万
 $18,768/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -31244,7 +31244,7 @@
           <t>N | 260呎 (1房)
 $510万
 $19,633/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -31252,7 +31252,7 @@
           <t>P | 314呎 (1房)
 $583万
 $18,565/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
@@ -31260,7 +31260,7 @@
           <t>Q | 430呎 (3房)
 $814万
 $18,922/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr">
@@ -31268,7 +31268,7 @@
           <t>R | 346呎 (2房)
 $659万
 $19,053/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="R17" s="20" t="inlineStr">
@@ -31276,7 +31276,7 @@
           <t>S | 269呎 (1房)
 $494万
 $18,362/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr">
@@ -31284,7 +31284,7 @@
           <t>T | 263呎 (1房)
 $514万
 $19,563/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="T17" s="20" t="inlineStr">
@@ -31292,7 +31292,7 @@
           <t>U | 262呎 (1房)
 $531万
 $20,258/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="U17" s="20" t="inlineStr">
@@ -31300,7 +31300,7 @@
           <t>V | 262呎 (1房)
 $506万
 $19,326/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="V17" s="20" t="inlineStr">
@@ -31308,7 +31308,7 @@
           <t>W | 270呎 (1房)
 $517万
 $19,157/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -31323,7 +31323,7 @@
           <t>A | 417呎 (2房)
 $832万
 $19,954/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -31331,7 +31331,7 @@
           <t>B | 369呎 (1房)
 $733万
 $19,859/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -31339,7 +31339,7 @@
           <t>C | 284呎 (1房)
 $545万
 $19,180/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -31347,7 +31347,7 @@
           <t>D | 411呎 (2房)
 $797万
 $19,399/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -31355,7 +31355,7 @@
           <t>E | 276呎 (1房)
 $535万
 $19,370/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -31363,7 +31363,7 @@
           <t>F | 266呎 (1房)
 $476万
 $17,900/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -31371,7 +31371,7 @@
           <t>G | 262呎 (1房)
 $522万
 $19,924/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -31379,7 +31379,7 @@
           <t>H | 262呎 (1房)
 $517万
 $19,725/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -31387,7 +31387,7 @@
           <t>J | 262呎 (1房)
 $490万
 $18,715/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -31395,7 +31395,7 @@
           <t>K | 262呎 (1房)
 $487万
 $18,588/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -31403,7 +31403,7 @@
           <t>L | 266呎 (1房)
 $492万
 $18,505/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -31411,7 +31411,7 @@
           <t>M | 266呎 (1房)
 $496万
 $18,655/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -31419,7 +31419,7 @@
           <t>N | 260呎 (1房)
 $507万
 $19,514/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -31427,7 +31427,7 @@
           <t>P | 314呎 (1房)
 $570万
 $18,145/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr">
@@ -31435,7 +31435,7 @@
           <t>Q | 430呎 (3房)
 $811万
 $18,865/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="Q18" s="20" t="inlineStr">
@@ -31443,7 +31443,7 @@
           <t>R | 346呎 (2房)
 $679万
 $19,629/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="R18" s="20" t="inlineStr">
@@ -31451,7 +31451,7 @@
           <t>S | 269呎 (1房)
 $482万
 $17,904/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="S18" s="20" t="inlineStr">
@@ -31459,7 +31459,7 @@
           <t>T | 263呎 (1房)
 $513万
 $19,503/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="T18" s="20" t="inlineStr">
@@ -31467,7 +31467,7 @@
           <t>U | 262呎 (1房)
 $527万
 $20,133/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="U18" s="20" t="inlineStr">
@@ -31475,7 +31475,7 @@
           <t>V | 262呎 (1房)
 $492万
 $18,781/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="V18" s="20" t="inlineStr">
@@ -31483,7 +31483,7 @@
           <t>W | 270呎 (1房)
 $514万
 $19,042/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
           <t>A | 417呎 (2房)
 $827万
 $19,833/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -31506,7 +31506,7 @@
           <t>B | 369呎 (1房)
 $768万
 $20,805/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -31514,7 +31514,7 @@
           <t>C | 284呎 (1房)
 $543万
 $19,123/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -31522,7 +31522,7 @@
           <t>D | 411呎 (2房)
 $795万
 $19,341/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -31530,7 +31530,7 @@
           <t>E | 276呎 (1房)
 $533万
 $19,311/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -31538,7 +31538,7 @@
           <t>F | 266呎 (1房)
 $475万
 $17,846/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -31546,7 +31546,7 @@
           <t>G | 262呎 (1房)
 $521万
 $19,867/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -31554,7 +31554,7 @@
           <t>H | 262呎 (1房)
 $515万
 $19,665/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -31562,7 +31562,7 @@
           <t>J | 262呎 (1房)
 $481万
 $18,348/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -31570,7 +31570,7 @@
           <t>K | 262呎 (1房)
 $486万
 $18,534/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -31578,7 +31578,7 @@
           <t>L | 266呎 (1房)
 $500万
 $18,804/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -31586,7 +31586,7 @@
           <t>M | 266呎 (1房)
 $510万
 $19,167/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -31594,7 +31594,7 @@
           <t>N | 260呎 (1房)
 $504万
 $19,391/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -31602,7 +31602,7 @@
           <t>P | 314呎 (1房)
 $566万
 $18,035/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr">
@@ -31610,7 +31610,7 @@
           <t>Q | 430呎 (3房)
 $809万
 $18,807/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="Q19" s="20" t="inlineStr">
@@ -31618,7 +31618,7 @@
           <t>R | 346呎 (2房)
 $644万
 $18,626/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="R19" s="20" t="inlineStr">
@@ -31626,7 +31626,7 @@
           <t>S | 269呎 (1房)
 $480万
 $17,848/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="S19" s="20" t="inlineStr">
@@ -31634,7 +31634,7 @@
           <t>T | 263呎 (1房)
 $511万
 $19,441/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="T19" s="20" t="inlineStr">
@@ -31642,7 +31642,7 @@
           <t>U | 262呎 (1房)
 $524万
 $20,005/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="U19" s="20" t="inlineStr">
@@ -31650,7 +31650,7 @@
           <t>V | 262呎 (1房)
 $489万
 $18,666/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="V19" s="20" t="inlineStr">
@@ -31658,7 +31658,7 @@
           <t>W | 270呎 (1房)
 $530万
 $19,619/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -31673,7 +31673,7 @@
           <t>A | 417呎 (2房)
 $825万
 $19,773/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -31681,7 +31681,7 @@
           <t>B | 369呎 (1房)
 $765万
 $20,742/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -31689,7 +31689,7 @@
           <t>C | 284呎 (1房)
 $547万
 $19,273/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -31697,7 +31697,7 @@
           <t>D | 411呎 (2房)
 $793万
 $19,282/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -31705,7 +31705,7 @@
           <t>E | 276呎 (1房)
 $528万
 $19,145/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -31713,7 +31713,7 @@
           <t>F | 266呎 (1房)
 $473万
 $17,789/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -31721,7 +31721,7 @@
           <t>G | 262呎 (1房)
 $509万
 $19,420/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -31729,7 +31729,7 @@
           <t>H | 262呎 (1房)
 $504万
 $19,253/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -31737,7 +31737,7 @@
           <t>J | 262呎 (1房)
 $493万
 $18,811/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -31745,7 +31745,7 @@
           <t>K | 262呎 (1房)
 $498万
 $19,002/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -31753,7 +31753,7 @@
           <t>L | 266呎 (1房)
 $499万
 $18,746/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -31761,7 +31761,7 @@
           <t>M | 266呎 (1房)
 $508万
 $19,108/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -31769,7 +31769,7 @@
           <t>N | 260呎 (1房)
 $503万
 $19,331/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -31777,7 +31777,7 @@
           <t>P | 314呎 (1房)
 $565万
 $17,979/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr">
@@ -31785,7 +31785,7 @@
           <t>Q | 430呎 (3房)
 $833万
 $19,383/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="Q20" s="20" t="inlineStr">
@@ -31793,7 +31793,7 @@
           <t>R | 346呎 (2房)
 $657万
 $18,989/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="R20" s="20" t="inlineStr">
@@ -31801,7 +31801,7 @@
           <t>S | 269呎 (1房)
 $479万
 $17,795/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="S20" s="20" t="inlineStr">
@@ -31809,7 +31809,7 @@
           <t>T | 263呎 (1房)
 $504万
 $19,170/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="T20" s="20" t="inlineStr">
@@ -31817,7 +31817,7 @@
           <t>U | 262呎 (1房)
 $523万
 $19,945/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="U20" s="20" t="inlineStr">
@@ -31825,7 +31825,7 @@
           <t>V | 262呎 (1房)
 $496万
 $18,924/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="V20" s="20" t="inlineStr">
@@ -31833,7 +31833,7 @@
           <t>W | 270呎 (1房)
 $528万
 $19,557/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -31848,7 +31848,7 @@
           <t>A | 417呎 (2房)
 $782万
 $18,759/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -31856,7 +31856,7 @@
           <t>B | 369呎 (1房)
 $738万
 $20,012/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -31864,7 +31864,7 @@
           <t>C | 284呎 (1房)
 $546万
 $19,215/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -31872,7 +31872,7 @@
           <t>D | 411呎 (2房)
 $790万
 $19,224/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -31880,7 +31880,7 @@
           <t>E | 276呎 (1房)
 $521万
 $18,870/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -31888,7 +31888,7 @@
           <t>F | 266呎 (1房)
 $472万
 $17,740/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -31896,7 +31896,7 @@
           <t>G | 262呎 (1房)
 $507万
 $19,363/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -31904,7 +31904,7 @@
           <t>H | 262呎 (1房)
 $503万
 $19,196/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -31912,7 +31912,7 @@
           <t>J | 262呎 (1房)
 $486万
 $18,550/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -31920,7 +31920,7 @@
           <t>K | 262呎 (1房)
 $483万
 $18,426/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -31928,7 +31928,7 @@
           <t>L | 266呎 (1房)
 $497万
 $18,685/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -31936,7 +31936,7 @@
           <t>M | 266呎 (1房)
 $507万
 $19,050/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -31944,7 +31944,7 @@
           <t>N | 260呎 (1房)
 $501万
 $19,268/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -31952,7 +31952,7 @@
           <t>P | 314呎 (1房)
 $563万
 $17,925/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
@@ -31960,7 +31960,7 @@
           <t>Q | 430呎 (3房)
 $831万
 $19,323/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="Q21" s="20" t="inlineStr">
@@ -31968,7 +31968,7 @@
           <t>R | 346呎 (2房)
 $641万
 $18,513/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="R21" s="20" t="inlineStr">
@@ -31976,7 +31976,7 @@
           <t>S | 269呎 (1房)
 $477万
 $17,743/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="S21" s="20" t="inlineStr">
@@ -31984,7 +31984,7 @@
           <t>T | 263呎 (1房)
 $508万
 $19,323/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="T21" s="20" t="inlineStr">
@@ -31992,7 +31992,7 @@
           <t>U | 262呎 (1房)
 $521万
 $19,881/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="U21" s="20" t="inlineStr">
@@ -32000,7 +32000,7 @@
           <t>V | 262呎 (1房)
 $486万
 $18,548/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="V21" s="20" t="inlineStr">
@@ -32008,7 +32008,7 @@
           <t>W | 270呎 (1房)
 $526万
 $19,499/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -32023,7 +32023,7 @@
           <t>A | 417呎 (2房)
 $822万
 $19,713/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -32031,7 +32031,7 @@
           <t>B | 369呎 (1房)
 $748万
 $20,284/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -32039,7 +32039,7 @@
           <t>C | 284呎 (1房)
 $526万
 $18,526/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -32047,7 +32047,7 @@
           <t>D | 411呎 (2房)
 $814万
 $19,816/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -32055,7 +32055,7 @@
           <t>E | 276呎 (1房)
 $519万
 $18,812/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -32063,7 +32063,7 @@
           <t>F | 266呎 (1房)
 $470万
 $17,680/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -32071,7 +32071,7 @@
           <t>G | 262呎 (1房)
 $506万
 $19,303/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -32079,7 +32079,7 @@
           <t>H | 262呎 (1房)
 $501万
 $19,136/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -32087,7 +32087,7 @@
           <t>J | 262呎 (1房)
 $476万
 $18,183/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -32095,7 +32095,7 @@
           <t>K | 262呎 (1房)
 $481万
 $18,369/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -32103,185 +32103,10 @@
           <t>L | 266呎 (1房)
 $495万
 $18,627/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
-        <is>
-          <t>M | 266呎 (1房)
-$505万
-$18,991/呎
-(25年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
-        <is>
-          <t>N | 260呎 (1房)
-$499万
-$19,208/呎
-(25年-10月-23日)</t>
-        </is>
-      </c>
-      <c r="O22" s="20" t="inlineStr">
-        <is>
-          <t>P | 314呎 (1房)
-$571万
-$18,172/呎
-(24年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="P22" s="20" t="inlineStr">
-        <is>
-          <t>Q | 430呎 (3房)
-$828万
-$19,264/呎
-(25年-10月-26日)</t>
-        </is>
-      </c>
-      <c r="Q22" s="20" t="inlineStr">
-        <is>
-          <t>R | 346呎 (2房)
-$653万
-$18,877/呎
-(25年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="R22" s="20" t="inlineStr">
-        <is>
-          <t>S | 269呎 (1房)
-$476万
-$17,693/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="S22" s="20" t="inlineStr">
-        <is>
-          <t>T | 263呎 (1房)
-$501万
-$19,053/呎
-(25年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="T22" s="20" t="inlineStr">
-        <is>
-          <t>U | 262呎 (1房)
-$519万
-$19,821/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="U22" s="20" t="inlineStr">
-        <is>
-          <t>V | 262呎 (1房)
-$484万
-$18,490/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="V22" s="20" t="inlineStr">
-        <is>
-          <t>W | 270呎 (1房)
-$525万
-$19,437/呎
-(26年-02月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$782万
-$18,759/呎
-(25年-10月-12日)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 369呎 (1房)
-$761万
-$20,616/呎
-(26年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
-$526万
-$18,526/呎
-(25年-09月-18日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 411呎 (2房)
-$814万
-$19,816/呎
-(25年-10月-27日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 276呎 (1房)
-$519万
-$18,812/呎
-(25年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$470万
-$17,680/呎
-(25年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 262呎 (1房)
-$498万
-$18,991/呎
-(25年-12月-11日)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>H | 262呎 (1房)
-$493万
-$18,827/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>J | 262呎 (1房)
-$476万
-$18,183/呎
-(25年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>K | 262呎 (1房)
-$481万
-$18,369/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>L | 266呎 (1房)
-$495万
-$18,627/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 266呎 (1房)
 $505万
@@ -32289,12 +32114,187 @@
 (25年-10月-16日)</t>
         </is>
       </c>
-      <c r="N23" s="20" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>N | 260呎 (1房)
 $499万
 $19,208/呎
-(25年-11月-03日)</t>
+(25年-10月-24日)</t>
+        </is>
+      </c>
+      <c r="O22" s="20" t="inlineStr">
+        <is>
+          <t>P | 314呎 (1房)
+$571万
+$18,172/呎
+(24年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="P22" s="20" t="inlineStr">
+        <is>
+          <t>Q | 430呎 (3房)
+$828万
+$19,264/呎
+(25年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="Q22" s="20" t="inlineStr">
+        <is>
+          <t>R | 346呎 (2房)
+$653万
+$18,877/呎
+(25年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="R22" s="20" t="inlineStr">
+        <is>
+          <t>S | 269呎 (1房)
+$476万
+$17,693/呎
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="S22" s="20" t="inlineStr">
+        <is>
+          <t>T | 263呎 (1房)
+$501万
+$19,053/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="T22" s="20" t="inlineStr">
+        <is>
+          <t>U | 262呎 (1房)
+$519万
+$19,821/呎
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="U22" s="20" t="inlineStr">
+        <is>
+          <t>V | 262呎 (1房)
+$484万
+$18,490/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="V22" s="20" t="inlineStr">
+        <is>
+          <t>W | 270呎 (1房)
+$525万
+$19,437/呎
+(26年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$782万
+$18,759/呎
+(25年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 369呎 (1房)
+$761万
+$20,616/呎
+(26年-01月-15日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+$526万
+$18,526/呎
+(25年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 411呎 (2房)
+$814万
+$19,816/呎
+(25年-10月-28日)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 276呎 (1房)
+$519万
+$18,812/呎
+(25年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$470万
+$17,680/呎
+(25年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 262呎 (1房)
+$498万
+$18,991/呎
+(25年-12月-12日)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$493万
+$18,827/呎
+(25年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 262呎 (1房)
+$476万
+$18,183/呎
+(25年-05月-16日)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 262呎 (1房)
+$481万
+$18,369/呎
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>L | 266呎 (1房)
+$495万
+$18,627/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>M | 266呎 (1房)
+$505万
+$18,991/呎
+(25年-10月-17日)</t>
+        </is>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>N | 260呎 (1房)
+$499万
+$19,208/呎
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -32302,7 +32302,7 @@
           <t>P | 314呎 (1房)
 $561万
 $17,869/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
@@ -32310,7 +32310,7 @@
           <t>Q | 430呎 (3房)
 $828万
 $19,264/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="Q23" s="20" t="inlineStr">
@@ -32318,7 +32318,7 @@
           <t>R | 346呎 (2房)
 $650万
 $18,773/呎
-(24年-08月-25日)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="R23" s="20" t="inlineStr">
@@ -32326,7 +32326,7 @@
           <t>S | 269呎 (1房)
 $476万
 $17,687/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="S23" s="20" t="inlineStr">
@@ -32334,7 +32334,7 @@
           <t>T | 263呎 (1房)
 $490万
 $18,632/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="T23" s="20" t="inlineStr">
@@ -32342,7 +32342,7 @@
           <t>U | 262呎 (1房)
 $519万
 $19,821/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="U23" s="20" t="inlineStr">
@@ -32350,7 +32350,7 @@
           <t>V | 262呎 (1房)
 $484万
 $18,490/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="V23" s="20" t="inlineStr">
@@ -32358,7 +32358,7 @@
           <t>W | 270呎 (1房)
 $525万
 $19,437/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -32373,7 +32373,7 @@
           <t>A | 417呎 (2房)
 $822万
 $19,713/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -32381,7 +32381,7 @@
           <t>B | 369呎 (1房)
 $756万
 $20,493/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -32389,7 +32389,7 @@
           <t>C | 284呎 (1房)
 $541万
 $19,035/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -32397,7 +32397,7 @@
           <t>D | 411呎 (2房)
 $810万
 $19,696/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -32405,7 +32405,7 @@
           <t>E | 276呎 (1房)
 $518万
 $18,755/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -32413,7 +32413,7 @@
           <t>F | 266呎 (1房)
 $469万
 $17,627/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -32421,7 +32421,7 @@
           <t>G | 262呎 (1房)
 $496万
 $18,935/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -32429,7 +32429,7 @@
           <t>H | 262呎 (1房)
 $492万
 $18,771/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -32437,7 +32437,7 @@
           <t>J | 262呎 (1房)
 $475万
 $18,129/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -32445,7 +32445,7 @@
           <t>K | 262呎 (1房)
 $480万
 $18,315/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -32453,7 +32453,7 @@
           <t>L | 266呎 (1房)
 $483万
 $18,159/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -32461,7 +32461,7 @@
           <t>M | 266呎 (1房)
 $487万
 $18,309/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -32469,7 +32469,7 @@
           <t>N | 260呎 (1房)
 $498万
 $19,148/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -32477,7 +32477,7 @@
           <t>P | 314呎 (1房)
 $571万
 $18,172/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr">
@@ -32485,7 +32485,7 @@
           <t>Q | 430呎 (3房)
 $801万
 $18,632/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="Q24" s="20" t="inlineStr">
@@ -32493,7 +32493,7 @@
           <t>R | 346呎 (2房)
 $648万
 $18,715/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="R24" s="20" t="inlineStr">
@@ -32501,7 +32501,7 @@
           <t>S | 269呎 (1房)
 $485万
 $18,033/呎
-(25年-02月-13日)</t>
+(25年-02月-14日)</t>
         </is>
       </c>
       <c r="S24" s="20" t="inlineStr">
@@ -32509,7 +32509,7 @@
           <t>T | 263呎 (1房)
 $488万
 $18,571/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="T24" s="20" t="inlineStr">
@@ -32517,7 +32517,7 @@
           <t>U | 262呎 (1房)
 $518万
 $19,757/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="U24" s="20" t="inlineStr">
@@ -32525,7 +32525,7 @@
           <t>V | 262呎 (1房)
 $483万
 $18,433/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="V24" s="20" t="inlineStr">
@@ -32533,7 +32533,7 @@
           <t>W | 270呎 (1房)
 $523万
 $19,375/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
     </row>
@@ -32548,7 +32548,7 @@
           <t>A | 417呎 (2房)
 $820万
 $19,653/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -32556,7 +32556,7 @@
           <t>B | 369呎 (1房)
 $739万
 $20,038/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -32564,7 +32564,7 @@
           <t>C | 284呎 (1房)
 $520万
 $18,295/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -32572,7 +32572,7 @@
           <t>D | 411呎 (2房)
 $813万
 $19,790/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -32580,7 +32580,7 @@
           <t>E | 276呎 (1房)
 $514万
 $18,636/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -32588,7 +32588,7 @@
           <t>F | 266呎 (1房)
 $474万
 $17,831/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -32596,7 +32596,7 @@
           <t>G | 262呎 (1房)
 $493万
 $18,824/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -32604,7 +32604,7 @@
           <t>H | 262呎 (1房)
 $489万
 $18,660/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -32612,7 +32612,7 @@
           <t>J | 262呎 (1房)
 $473万
 $18,061/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -32620,7 +32620,7 @@
           <t>K | 262呎 (1房)
 $477万
 $18,206/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -32628,7 +32628,7 @@
           <t>L | 266呎 (1房)
 $480万
 $18,053/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -32636,7 +32636,7 @@
           <t>M | 266呎 (1房)
 $484万
 $18,195/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -32644,7 +32644,7 @@
           <t>N | 260呎 (1房)
 $496万
 $19,078/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr">
@@ -32652,7 +32652,7 @@
           <t>P | 314呎 (1房)
 $561万
 $17,869/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
@@ -32660,7 +32660,7 @@
           <t>Q | 430呎 (3房)
 $801万
 $18,632/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="Q25" s="20" t="inlineStr">
@@ -32668,7 +32668,7 @@
           <t>R | 346呎 (2房)
 $646万
 $18,661/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="R25" s="20" t="inlineStr">
@@ -32676,7 +32676,7 @@
           <t>S | 269呎 (1房)
 $473万
 $17,578/呎
-(25年-01月-20日)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="S25" s="20" t="inlineStr">
@@ -32684,7 +32684,7 @@
           <t>T | 263呎 (1房)
 $487万
 $18,514/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="T25" s="20" t="inlineStr">
@@ -32692,7 +32692,7 @@
           <t>U | 262呎 (1房)
 $527万
 $20,117/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="U25" s="20" t="inlineStr">
@@ -32700,7 +32700,7 @@
           <t>V | 262呎 (1房)
 $490万
 $18,687/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="V25" s="20" t="inlineStr">
@@ -32708,7 +32708,7 @@
           <t>W | 270呎 (1房)
 $522万
 $19,323/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -32723,7 +32723,7 @@
           <t>A | 379呎 (2房)
 $940万
 $24,800/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -32731,7 +32731,7 @@
           <t>B | 331呎 (1房)
 $828万
 $25,000/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -32739,7 +32739,7 @@
           <t>C | 246呎 (1房)
 $635万
 $25,800/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -32747,7 +32747,7 @@
           <t>D | 373呎 (2房)
 $910万
 $24,400/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -32755,7 +32755,7 @@
           <t>E | 239呎 (1房)
 $586万
 $24,500/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -32763,7 +32763,7 @@
           <t>F | 228呎 (1房)
 $554万
 $24,300/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -32771,7 +32771,7 @@
           <t>G | 225呎 (1房)
 $528万
 $23,467/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -32779,7 +32779,7 @@
           <t>H | 225呎 (1房)
 $538万
 $23,900/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -32787,7 +32787,7 @@
           <t>J | 225呎 (1房)
 $538万
 $23,900/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -32795,7 +32795,7 @@
           <t>K | 225呎 (1房)
 $544万
 $24,200/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -32803,7 +32803,7 @@
           <t>L | 228呎 (1房)
 $523万
 $22,924/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -32811,7 +32811,7 @@
           <t>M | 228呎 (1房)
 $538万
 $23,587/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -32819,7 +32819,7 @@
           <t>N | 223呎 (1房)
 $546万
 $24,500/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="O26" s="20" t="inlineStr">
@@ -32827,7 +32827,7 @@
           <t>P | 276呎 (1房)
 $701万
 $25,400/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="P26" s="20" t="inlineStr">
@@ -32835,7 +32835,7 @@
           <t>Q | 392呎 (3房)
 $980万
 $25,000/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="Q26" s="20" t="inlineStr">
@@ -32843,7 +32843,7 @@
           <t>R | 309呎 (2房)
 $779万
 $25,200/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="R26" s="20" t="inlineStr">
@@ -32851,7 +32851,7 @@
           <t>S | 229呎 (1房)
 $614万
 $26,800/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="S26" s="20" t="inlineStr">
@@ -32859,7 +32859,7 @@
           <t>T | 225呎 (1房)
 $578万
 $25,700/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="T26" s="20" t="inlineStr">
@@ -32867,7 +32867,7 @@
           <t>U | 224呎 (1房)
 $573万
 $25,600/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="U26" s="20" t="inlineStr">
@@ -32875,7 +32875,7 @@
           <t>V | 224呎 (1房)
 $571万
 $25,500/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="V26" s="20" t="inlineStr">
@@ -32883,7 +32883,7 @@
           <t>W | 233呎 (1房)
 $580万
 $24,900/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -17002,7 +17002,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -31164,7 +31164,7 @@
           <t>C | 284呎 (1房)
 $536万
 $18,871/呎
-(26年-01月-15日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">

--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>5784300</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>18421</v>
+        <v>18480</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>5784300</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>18421</v>
+        <v>18480</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -30899,9 +30899,9 @@
       </c>
       <c r="O15" s="20" t="inlineStr">
         <is>
-          <t>P | 314呎 (1房)
+          <t>P | 313呎 (1房)
 $578万
-$18,421/呎
+$18,480/呎
 (25年-03月-14日)</t>
         </is>
       </c>
@@ -31164,7 +31164,7 @@
           <t>C | 284呎 (1房)
 $536万
 $18,871/呎
-(25年-08月-21日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
